--- a/Masy.xlsx
+++ b/Masy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B8DE79-2804-4C5C-99EA-3809BE1C5062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C5DD78-DB65-4D1C-A2A6-5F5AA1D8AE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{1B89EA85-0D7B-4BD5-90E2-014B62B41C6E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Nazwa</t>
   </si>
@@ -153,9 +153,6 @@
   </si>
   <si>
     <t>Koło</t>
-  </si>
-  <si>
-    <t>Front mount, Aluminium (teoria)</t>
   </si>
 </sst>
 </file>
@@ -596,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10803BC4-6355-4647-A605-F1E7D1B0F2BA}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -736,7 +733,7 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -751,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -766,7 +763,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -824,7 +821,7 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -858,13 +855,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="C18" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -872,151 +869,152 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>136</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C19" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B20" s="3">
-        <v>4.0999999999999996</v>
+        <v>39</v>
       </c>
       <c r="C20" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>39</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C21" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B22" s="3">
-        <v>4.0999999999999996</v>
+        <v>39</v>
       </c>
       <c r="C22" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>39</v>
+        <v>8.1</v>
       </c>
       <c r="C23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>8.1</v>
+        <v>70.5</v>
       </c>
       <c r="C24" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B25" s="3">
-        <v>70.5</v>
+        <v>8.1</v>
       </c>
       <c r="C25" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B26" s="3">
-        <v>8.1</v>
+        <v>70.5</v>
       </c>
       <c r="C26" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B27" s="3">
-        <v>70.5</v>
+        <v>1</v>
       </c>
       <c r="C27" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <f>3.3/2</f>
+        <v>1.65</v>
       </c>
       <c r="C28" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" s="3">
-        <f>3.3/2</f>
-        <v>1.65</v>
+        <f>21.6/2</f>
+        <v>10.8</v>
       </c>
       <c r="C29" s="4">
         <v>2</v>
@@ -1027,11 +1025,11 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="3">
-        <f>21.6/2</f>
-        <v>10.8</v>
+        <f>6.6/2</f>
+        <v>3.3</v>
       </c>
       <c r="C30" s="4">
         <v>2</v>
@@ -1042,11 +1040,11 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="3">
-        <f>6.6/2</f>
-        <v>3.3</v>
+        <f>1.6/2</f>
+        <v>0.8</v>
       </c>
       <c r="C31" s="4">
         <v>2</v>
@@ -1057,11 +1055,11 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="3">
-        <f>1.6/2</f>
-        <v>0.8</v>
+        <f>1/2</f>
+        <v>0.5</v>
       </c>
       <c r="C32" s="4">
         <v>2</v>
@@ -1072,72 +1070,57 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B33" s="3">
-        <f>1/2</f>
-        <v>0.5</v>
+        <v>39</v>
       </c>
       <c r="C33" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B34" s="3">
-        <v>39</v>
+        <v>22.5</v>
       </c>
       <c r="C34" s="4">
         <v>1</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="3">
-        <v>22.5</v>
+        <v>53</v>
       </c>
       <c r="C35" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="3">
-        <v>53</v>
-      </c>
-      <c r="C36" s="4">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="3">
-        <f>SUMPRODUCT(B2:B39,C2:C39)</f>
-        <v>861.82333333333338</v>
-      </c>
-      <c r="D40" s="3">
-        <f>SUMPRODUCT(B2:B39,D2:D39)</f>
-        <v>502.52333333333348</v>
+      <c r="C39" s="3">
+        <f>SUMPRODUCT(B2:B38,C2:C38)</f>
+        <v>845.32333333333338</v>
+      </c>
+      <c r="D39" s="3">
+        <f>SUMPRODUCT(B2:B38,D2:D38)</f>
+        <v>445.59000000000015</v>
       </c>
     </row>
   </sheetData>

--- a/Masy.xlsx
+++ b/Masy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C5DD78-DB65-4D1C-A2A6-5F5AA1D8AE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65345E0-24FF-4381-A21B-3CA27883CC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{1B89EA85-0D7B-4BD5-90E2-014B62B41C6E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Nazwa</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>Koło</t>
+  </si>
+  <si>
+    <t>Front mount, ALU</t>
   </si>
 </sst>
 </file>
@@ -593,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10803BC4-6355-4647-A605-F1E7D1B0F2BA}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -644,7 +647,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="5"/>
     </row>
@@ -748,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -763,7 +766,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -821,7 +824,7 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -855,272 +858,286 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="C18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>4.0999999999999996</v>
+        <v>136</v>
       </c>
       <c r="C19" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>39</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C20" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>4.0999999999999996</v>
+        <v>39</v>
       </c>
       <c r="C21" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B22" s="3">
-        <v>39</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B23" s="3">
-        <v>8.1</v>
+        <v>39</v>
       </c>
       <c r="C23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="3">
-        <v>70.5</v>
+        <v>8.1</v>
       </c>
       <c r="C24" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B25" s="3">
-        <v>8.1</v>
+        <v>70.5</v>
       </c>
       <c r="C25" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>70.5</v>
+        <v>8.1</v>
       </c>
       <c r="C26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>70.5</v>
       </c>
       <c r="C27" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B29" s="3">
         <f>3.3/2</f>
         <v>1.65</v>
       </c>
-      <c r="C28" s="4">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <f>21.6/2</f>
         <v>10.8</v>
       </c>
-      <c r="C29" s="4">
-        <v>2</v>
-      </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
+      <c r="C30" s="4">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B31" s="3">
         <f>6.6/2</f>
         <v>3.3</v>
       </c>
-      <c r="C30" s="4">
-        <v>2</v>
-      </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
+      <c r="C31" s="4">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B32" s="3">
         <f>1.6/2</f>
         <v>0.8</v>
       </c>
-      <c r="C31" s="4">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
+      <c r="C32" s="4">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B33" s="3">
         <f>1/2</f>
         <v>0.5</v>
       </c>
-      <c r="C32" s="4">
-        <v>2</v>
-      </c>
-      <c r="D32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="3">
-        <v>39</v>
-      </c>
       <c r="C33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B34" s="3">
-        <v>22.5</v>
+        <v>39</v>
       </c>
       <c r="C34" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3">
+        <v>22.5</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B36" s="3">
         <v>53</v>
       </c>
-      <c r="C35" s="4">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="3">
-        <f>SUMPRODUCT(B2:B38,C2:C38)</f>
+      <c r="C40" s="3">
+        <f>SUMPRODUCT(B2:B39,C2:C39)</f>
         <v>845.32333333333338</v>
       </c>
-      <c r="D39" s="3">
-        <f>SUMPRODUCT(B2:B38,D2:D38)</f>
-        <v>445.59000000000015</v>
+      <c r="D40" s="3">
+        <f>SUMPRODUCT(B2:B39,D2:D39)</f>
+        <v>484.32333333333349</v>
       </c>
     </row>
   </sheetData>
